--- a/Data/Rules/Kennel Master Rules Matrix.xlsx
+++ b/Data/Rules/Kennel Master Rules Matrix.xlsx
@@ -664,10 +664,10 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -685,7 +685,7 @@
         <v>5</v>
       </c>
       <c r="Y2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="AE2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
@@ -750,10 +750,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
@@ -840,10 +840,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="b">
         <v>1</v>
@@ -872,19 +872,19 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="b">
         <v>0</v>
@@ -899,19 +899,19 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -944,10 +944,10 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
@@ -962,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="b">
         <v>1</v>

--- a/Data/Rules/Kennel Master Rules Matrix.xlsx
+++ b/Data/Rules/Kennel Master Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>12378</t>
@@ -486,10 +489,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AO4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -610,16 +613,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -732,16 +738,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>51</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -854,16 +863,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>59</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -975,6 +987,9 @@
       </c>
       <c r="AN4">
         <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
